--- a/九龙-启德-柏蔚森 III/柏蔚森 III_销控明细表.xlsx
+++ b/九龙-启德-柏蔚森 III/柏蔚森 III_销控明细表.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10630,7 +10630,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12490,7 +12490,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14288,7 +14288,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14846,7 +14846,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15404,7 +15404,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15652,7 +15652,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15776,7 +15776,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15962,7 +15962,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16024,7 +16024,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16334,7 +16334,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16768,7 +16768,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16830,7 +16830,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17264,7 +17264,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17326,7 +17326,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17589,7 +17589,7 @@
           <t>H | 394呎 (2房)
 $746万
 $18,921/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -17597,7 +17597,7 @@
           <t>J | 261呎 (1房)
 $497万
 $19,042/呎
-(24年-10月-03日)</t>
+(24年-10月-04日)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
@@ -17605,7 +17605,7 @@
           <t>K | 260呎 (1房)
 $499万
 $19,181/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -17652,7 +17652,7 @@
           <t>D | 263呎 (1房)
 $524万
 $19,909/呎
-(24年-09月-25日)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -17684,7 +17684,7 @@
           <t>H | 394呎 (2房)
 $738万
 $18,736/呎
-(24年-08月-20日)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -17692,7 +17692,7 @@
           <t>J | 261呎 (1房)
 $495万
 $18,966/呎
-(24年-09月-23日)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -17700,7 +17700,7 @@
           <t>K | 260呎 (1房)
 $494万
 $18,988/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
@@ -17708,7 +17708,7 @@
           <t>L | 390呎 (2房)
 $716万
 $18,349/呎
-(24年-08月-18日)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -17747,7 +17747,7 @@
           <t>D | 263呎 (1房)
 $519万
 $19,719/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -17779,7 +17779,7 @@
           <t>H | 394呎 (2房)
 $734万
 $18,642/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -17787,7 +17787,7 @@
           <t>J | 261呎 (1房)
 $496万
 $18,996/呎
-(24年-09月-11日)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -17795,7 +17795,7 @@
           <t>K | 260呎 (1房)
 $486万
 $18,692/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
@@ -17803,7 +17803,7 @@
           <t>L | 390呎 (2房)
 $712万
 $18,259/呎
-(24年-08月-20日)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
           <t>D | 263呎 (1房)
 $511万
 $19,418/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -17850,7 +17850,7 @@
           <t>E | 383呎 (2房)
 $939万
 $24,520/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -17858,7 +17858,7 @@
           <t>F | 382呎 (2房)
 $871万
 $22,801/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -17866,7 +17866,7 @@
           <t>G | 395呎 (2房)
 $897万
 $22,701/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -17874,7 +17874,7 @@
           <t>H | 394呎 (2房)
 $731万
 $18,548/呎
-(24年-09月-12日)</t>
+(24年-09月-13日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -17882,7 +17882,7 @@
           <t>J | 261呎 (1房)
 $493万
 $18,900/呎
-(24年-09月-09日)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -17890,7 +17890,7 @@
           <t>K | 260呎 (1房)
 $484万
 $18,600/呎
-(24年-10月-21日)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
@@ -17898,7 +17898,7 @@
           <t>L | 390呎 (2房)
 $708万
 $18,167/呎
-(24年-08月-15日)</t>
+(24年-08月-16日)</t>
         </is>
       </c>
     </row>
@@ -17937,7 +17937,7 @@
           <t>D | 263呎 (1房)
 $506万
 $19,224/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -17945,7 +17945,7 @@
           <t>E | 383呎 (2房)
 $862万
 $22,496/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -17953,7 +17953,7 @@
           <t>F | 382呎 (2房)
 $843万
 $22,071/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -17961,7 +17961,7 @@
           <t>G | 395呎 (2房)
 $888万
 $22,476/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -17969,7 +17969,7 @@
           <t>H | 394呎 (2房)
 $727万
 $18,457/呎
-(24年-08月-19日)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -17977,7 +17977,7 @@
           <t>J | 261呎 (1房)
 $491万
 $18,805/呎
-(24年-09月-08日)</t>
+(24年-09月-09日)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -17985,7 +17985,7 @@
           <t>K | 260呎 (1房)
 $481万
 $18,508/呎
-(24年-10月-06日)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
@@ -17993,7 +17993,7 @@
           <t>L | 390呎 (2房)
 $706万
 $18,113/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -18008,7 +18008,7 @@
           <t>A | 666呎 (3房)
 $1964万
 $29,488/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -18032,7 +18032,7 @@
           <t>D | 263呎 (1房)
 $503万
 $19,125/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -18040,7 +18040,7 @@
           <t>E | 383呎 (2房)
 $885万
 $23,110/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -18048,7 +18048,7 @@
           <t>F | 382呎 (2房)
 $842万
 $22,050/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -18056,7 +18056,7 @@
           <t>G | 395呎 (2房)
 $838万
 $21,203/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -18064,7 +18064,7 @@
           <t>H | 394呎 (2房)
 $725万
 $18,404/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
@@ -18072,7 +18072,7 @@
           <t>J | 261呎 (1房)
 $488万
 $18,713/呎
-(24年-08月-22日)</t>
+(24年-08月-23日)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -18080,7 +18080,7 @@
           <t>K | 260呎 (1房)
 $499万
 $19,208/呎
-(24年-09月-23日)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
@@ -18088,7 +18088,7 @@
           <t>L | 390呎 (2房)
 $704万
 $18,056/呎
-(24年-08月-13日)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -18119,7 +18119,7 @@
           <t>C | 579呎 (3房)
 $1514万
 $26,154/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -18127,7 +18127,7 @@
           <t>D | 263呎 (1房)
 $503万
 $19,137/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -18135,7 +18135,7 @@
           <t>E | 383呎 (2房)
 $812万
 $21,204/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -18143,7 +18143,7 @@
           <t>F | 382呎 (2房)
 $795万
 $20,801/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -18151,7 +18151,7 @@
           <t>G | 395呎 (2房)
 $813万
 $20,587/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -18159,7 +18159,7 @@
           <t>H | 394呎 (2房)
 $720万
 $18,277/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -18167,7 +18167,7 @@
           <t>J | 261呎 (1房)
 $486万
 $18,621/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -18175,7 +18175,7 @@
           <t>K | 260呎 (1房)
 $479万
 $18,427/呎
-(24年-09月-10日)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -18183,7 +18183,7 @@
           <t>L | 390呎 (2房)
 $732万
 $18,772/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
     </row>
@@ -18206,7 +18206,7 @@
           <t>B | 382呎 (2房)
 $990万
 $25,919/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -18214,7 +18214,7 @@
           <t>C | 579呎 (3房)
 $1556万
 $26,870/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -18222,7 +18222,7 @@
           <t>D | 263呎 (1房)
 $498万
 $18,935/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -18230,7 +18230,7 @@
           <t>E | 383呎 (2房)
 $783万
 $20,446/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -18238,7 +18238,7 @@
           <t>F | 382呎 (2房)
 $769万
 $20,136/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -18246,7 +18246,7 @@
           <t>G | 395呎 (2房)
 $787万
 $19,929/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -18254,7 +18254,7 @@
           <t>H | 394呎 (2房)
 $718万
 $18,221/呎
-(24年-10月-13日)</t>
+(24年-10月-14日)</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -18262,7 +18262,7 @@
           <t>J | 261呎 (1房)
 $484万
 $18,529/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -18270,7 +18270,7 @@
           <t>K | 260呎 (1房)
 $477万
 $18,338/呎
-(24年-08月-29日)</t>
+(24年-08月-30日)</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
@@ -18278,7 +18278,7 @@
           <t>L | 390呎 (2房)
 $747万
 $19,156/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -18293,7 +18293,7 @@
           <t>A | 666呎 (3房)
 $1698万
 $25,500/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -18309,7 +18309,7 @@
           <t>C | 579呎 (3房)
 $1427万
 $24,653/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -18317,7 +18317,7 @@
           <t>D | 263呎 (1房)
 $496万
 $18,840/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -18325,7 +18325,7 @@
           <t>E | 383呎 (2房)
 $763万
 $19,927/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -18333,7 +18333,7 @@
           <t>F | 382呎 (2房)
 $747万
 $19,550/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -18341,7 +18341,7 @@
           <t>G | 395呎 (2房)
 $764万
 $19,347/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -18349,7 +18349,7 @@
           <t>H | 394呎 (2房)
 $749万
 $19,015/呎
-(24年-08月-27日)</t>
+(24年-08月-28日)</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
@@ -18357,7 +18357,7 @@
           <t>J | 261呎 (1房)
 $502万
 $19,222/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -18365,7 +18365,7 @@
           <t>K | 260呎 (1房)
 $474万
 $18,246/呎
-(24年-09月-02日)</t>
+(24年-09月-03日)</t>
         </is>
       </c>
       <c r="L13" s="22" t="inlineStr">
@@ -18373,7 +18373,7 @@
           <t>L | 390呎 (2房)
 $728万
 $18,662/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
     </row>
@@ -18388,7 +18388,7 @@
           <t>A | 666呎 (3房)
 $1756万
 $26,362/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -18404,7 +18404,7 @@
           <t>C | 579呎 (3房)
 $1386万
 $23,934/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -18412,7 +18412,7 @@
           <t>D | 263呎 (1房)
 $496万
 $18,856/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -18420,7 +18420,7 @@
           <t>E | 383呎 (2房)
 $741万
 $19,347/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -18428,7 +18428,7 @@
           <t>F | 382呎 (2房)
 $725万
 $18,982/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -18436,7 +18436,7 @@
           <t>G | 395呎 (2房)
 $742万
 $18,787/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -18444,7 +18444,7 @@
           <t>H | 394呎 (2房)
 $716万
 $18,183/呎
-(24年-08月-20日)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -18452,7 +18452,7 @@
           <t>J | 261呎 (1房)
 $499万
 $19,126/呎
-(24年-08月-15日)</t>
+(24年-08月-16日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -18460,7 +18460,7 @@
           <t>K | 260呎 (1房)
 $600万
 $23,062/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
@@ -18468,7 +18468,7 @@
           <t>L | 390呎 (2房)
 $694万
 $17,800/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -18483,7 +18483,7 @@
           <t>A | 666呎 (3房)
 $1626万
 $24,410/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -18491,7 +18491,7 @@
           <t>B | 382呎 (2房)
 $947万
 $24,788/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -18499,7 +18499,7 @@
           <t>C | 579呎 (3房)
 $1352万
 $23,349/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -18507,7 +18507,7 @@
           <t>D | 263呎 (1房)
 $490万
 $18,650/呎
-(24年-10月-16日)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -18515,7 +18515,7 @@
           <t>E | 383呎 (2房)
 $703万
 $18,350/呎
-(24年-10月-17日)</t>
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -18523,7 +18523,7 @@
           <t>F | 382呎 (2房)
 $717万
 $18,772/呎
-(24年-09月-26日)</t>
+(24年-09月-27日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -18531,7 +18531,7 @@
           <t>G | 395呎 (2房)
 $704万
 $17,818/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -18539,7 +18539,7 @@
           <t>H | 394呎 (2房)
 $745万
 $18,901/呎
-(24年-08月-14日)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -18547,7 +18547,7 @@
           <t>J | 261呎 (1房)
 $476万
 $18,253/呎
-(25年-02月-25日)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -18555,7 +18555,7 @@
           <t>K | 260呎 (1房)
 $470万
 $18,065/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -18563,7 +18563,7 @@
           <t>L | 390呎 (2房)
 $687万
 $17,623/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
           <t>A | 666呎 (3房)
 $1594万
 $23,932/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -18586,7 +18586,7 @@
           <t>B | 382呎 (2房)
 $906万
 $23,720/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -18594,7 +18594,7 @@
           <t>C | 579呎 (3房)
 $1332万
 $23,005/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -18602,7 +18602,7 @@
           <t>D | 263呎 (1房)
 $488万
 $18,559/呎
-(24年-10月-16日)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -18610,7 +18610,7 @@
           <t>E | 383呎 (2房)
 $699万
 $18,261/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -18618,7 +18618,7 @@
           <t>F | 382呎 (2房)
 $684万
 $17,914/呎
-(24年-09月-24日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -18626,7 +18626,7 @@
           <t>G | 395呎 (2房)
 $700万
 $17,729/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -18634,7 +18634,7 @@
           <t>H | 394呎 (2房)
 $712万
 $18,074/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -18642,7 +18642,7 @@
           <t>J | 261呎 (1房)
 $472万
 $18,073/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -18650,7 +18650,7 @@
           <t>K | 260呎 (1房)
 $465万
 $17,885/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -18658,7 +18658,7 @@
           <t>L | 390呎 (2房)
 $710万
 $18,195/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
     </row>
@@ -18673,7 +18673,7 @@
           <t>A | 666呎 (3房)
 $1563万
 $23,462/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -18681,7 +18681,7 @@
           <t>B | 382呎 (2房)
 $867万
 $22,696/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -18689,7 +18689,7 @@
           <t>C | 579呎 (3房)
 $1312万
 $22,665/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -18697,7 +18697,7 @@
           <t>D | 263呎 (1房)
 $486万
 $18,464/呎
-(24年-10月-09日)</t>
+(24年-10月-10日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -18705,7 +18705,7 @@
           <t>E | 383呎 (2房)
 $696万
 $18,170/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -18713,7 +18713,7 @@
           <t>F | 382呎 (2房)
 $681万
 $17,825/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -18721,7 +18721,7 @@
           <t>G | 395呎 (2房)
 $697万
 $17,641/呎
-(24年-10月-20日)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -18729,7 +18729,7 @@
           <t>H | 394呎 (2房)
 $710万
 $18,020/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -18737,7 +18737,7 @@
           <t>J | 261呎 (1房)
 $470万
 $18,019/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -18745,7 +18745,7 @@
           <t>K | 260呎 (1房)
 $464万
 $17,831/呎
-(24年-08月-15日)</t>
+(24年-08月-16日)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -18753,7 +18753,7 @@
           <t>L | 390呎 (2房)
 $678万
 $17,397/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
           <t>A | 666呎 (3房)
 $1532万
 $23,002/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -18784,7 +18784,7 @@
           <t>C | 579呎 (3房)
 $1247万
 $21,537/呎
-(24年-10月-03日)</t>
+(24年-10月-04日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -18792,7 +18792,7 @@
           <t>D | 263呎 (1房)
 $480万
 $18,232/呎
-(24年-08月-21日)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -18800,7 +18800,7 @@
           <t>E | 383呎 (2房)
 $692万
 $18,063/呎
-(24年-09月-04日)</t>
+(24年-09月-05日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -18808,7 +18808,7 @@
           <t>F | 382呎 (2房)
 $677万
 $17,712/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -18816,7 +18816,7 @@
           <t>G | 395呎 (2房)
 $693万
 $17,537/呎
-(24年-09月-16日)</t>
+(24年-09月-17日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -18824,7 +18824,7 @@
           <t>H | 394呎 (2房)
 $708万
 $17,967/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -18832,7 +18832,7 @@
           <t>J | 261呎 (1房)
 $469万
 $17,966/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -18840,7 +18840,7 @@
           <t>K | 260呎 (1房)
 $462万
 $17,781/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -18848,7 +18848,7 @@
           <t>L | 390呎 (2房)
 $705万
 $18,087/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -18863,7 +18863,7 @@
           <t>A | 666呎 (3房)
 $1502万
 $22,550/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -18871,7 +18871,7 @@
           <t>B | 382呎 (2房)
 $838万
 $21,924/呎
-(24年-08月-13日)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -18879,7 +18879,7 @@
           <t>C | 579呎 (3房)
 $1239万
 $21,404/呎
-(24年-08月-13日)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -18887,7 +18887,7 @@
           <t>D | 263呎 (1房)
 $477万
 $18,144/呎
-(24年-09月-02日)</t>
+(24年-09月-03日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -18895,7 +18895,7 @@
           <t>E | 383呎 (2房)
 $688万
 $17,971/呎
-(24年-09月-09日)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -18903,7 +18903,7 @@
           <t>F | 382呎 (2房)
 $673万
 $17,623/呎
-(24年-08月-19日)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -18911,7 +18911,7 @@
           <t>G | 395呎 (2房)
 $686万
 $17,377/呎
-(24年-10月-03日)</t>
+(24年-10月-04日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -18919,7 +18919,7 @@
           <t>H | 394呎 (2房)
 $706万
 $17,911/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -18927,7 +18927,7 @@
           <t>J | 261呎 (1房)
 $468万
 $17,912/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -18935,7 +18935,7 @@
           <t>K | 260呎 (1房)
 $461万
 $17,727/呎
-(24年-08月-20日)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -18943,7 +18943,7 @@
           <t>L | 390呎 (2房)
 $674万
 $17,290/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -18958,7 +18958,7 @@
           <t>A | 666呎 (3房)
 $1470万
 $22,069/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -18966,7 +18966,7 @@
           <t>B | 382呎 (2房)
 $812万
 $21,254/呎
-(24年-08月-18日)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -18974,7 +18974,7 @@
           <t>C | 579呎 (3房)
 $1218万
 $21,033/呎
-(25年-05月-13日)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -18982,7 +18982,7 @@
           <t>D | 263呎 (1房)
 $475万
 $18,053/呎
-(24年-09月-03日)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -18990,7 +18990,7 @@
           <t>E | 383呎 (2房)
 $685万
 $17,883/呎
-(24年-09月-16日)</t>
+(24年-09月-17日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -18998,7 +18998,7 @@
           <t>F | 382呎 (2房)
 $670万
 $17,534/呎
-(24年-08月-29日)</t>
+(24年-08月-30日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -19006,7 +19006,7 @@
           <t>G | 395呎 (2房)
 $686万
 $17,362/呎
-(24年-09月-03日)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -19014,7 +19014,7 @@
           <t>H | 394呎 (2房)
 $692万
 $17,561/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -19022,7 +19022,7 @@
           <t>J | 261呎 (1房)
 $458万
 $17,559/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -19030,7 +19030,7 @@
           <t>K | 260呎 (1房)
 $452万
 $17,381/呎
-(24年-08月-15日)</t>
+(24年-08月-16日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -19038,7 +19038,7 @@
           <t>L | 390呎 (2房)
 $670万
 $17,169/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -19053,7 +19053,7 @@
           <t>A | 666呎 (3房)
 $1461万
 $21,932/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -19061,7 +19061,7 @@
           <t>B | 382呎 (2房)
 $808万
 $21,147/呎
-(24年-08月-20日)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -19069,7 +19069,7 @@
           <t>C | 579呎 (3房)
 $1224万
 $21,149/呎
-(24年-08月-13日)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -19077,7 +19077,7 @@
           <t>D | 263呎 (1房)
 $472万
 $17,966/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -19085,7 +19085,7 @@
           <t>E | 383呎 (2房)
 $682万
 $17,794/呎
-(24年-08月-15日)</t>
+(24年-08月-16日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -19093,7 +19093,7 @@
           <t>F | 382呎 (2房)
 $666万
 $17,448/呎
-(24年-08月-18日)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -19101,7 +19101,7 @@
           <t>G | 395呎 (2房)
 $712万
 $18,015/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -19109,7 +19109,7 @@
           <t>H | 394呎 (2房)
 $707万
 $17,954/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -19117,7 +19117,7 @@
           <t>J | 261呎 (1房)
 $468万
 $17,946/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -19125,7 +19125,7 @@
           <t>K | 260呎 (1房)
 $443万
 $17,038/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -19133,7 +19133,7 @@
           <t>L | 390呎 (2房)
 $670万
 $17,187/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
     </row>
@@ -19148,7 +19148,7 @@
           <t>A | 666呎 (3房)
 $1426万
 $21,416/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -19156,7 +19156,7 @@
           <t>B | 382呎 (2房)
 $838万
 $21,940/呎
-(24年-08月-20日)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -19164,7 +19164,7 @@
           <t>C | 579呎 (3房)
 $1216万
 $20,997/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -19172,7 +19172,7 @@
           <t>D | 263呎 (1房)
 $598万
 $22,745/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -19180,7 +19180,7 @@
           <t>E | 383呎 (2房)
 $680万
 $17,742/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -19188,7 +19188,7 @@
           <t>F | 382呎 (2房)
 $693万
 $18,136/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -19196,7 +19196,7 @@
           <t>G | 395呎 (2房)
 $680万
 $17,223/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -19204,7 +19204,7 @@
           <t>H | 394呎 (2房)
 $665万
 $16,878/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -19212,7 +19212,7 @@
           <t>J | 261呎 (1房)
 $440万
 $16,877/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -19220,7 +19220,7 @@
           <t>K | 260呎 (1房)
 $453万
 $17,415/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -19228,7 +19228,7 @@
           <t>L | 390呎 (2房)
 $842万
 $21,595/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -19243,7 +19243,7 @@
           <t>A | 666呎 (3房)
 $1418万
 $21,288/呎
-(24年-08月-20日)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19251,7 +19251,7 @@
           <t>B | 382呎 (2房)
 $800万
 $20,937/呎
-(24年-08月-14日)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -19259,7 +19259,7 @@
           <t>C | 579呎 (3房)
 $1212万
 $20,940/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -19267,7 +19267,7 @@
           <t>D | 263呎 (1房)
 $470万
 $17,856/呎
-(24年-08月-13日)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -19275,7 +19275,7 @@
           <t>E | 383呎 (2房)
 $706万
 $18,444/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -19283,7 +19283,7 @@
           <t>F | 382呎 (2房)
 $663万
 $17,346/呎
-(24年-08月-22日)</t>
+(24年-08月-23日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -19291,7 +19291,7 @@
           <t>G | 395呎 (2房)
 $676万
 $17,101/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -19299,7 +19299,7 @@
           <t>H | 394呎 (2房)
 $663万
 $16,830/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -19307,7 +19307,7 @@
           <t>J | 261呎 (1房)
 $439万
 $16,828/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -19315,7 +19315,7 @@
           <t>K | 260呎 (1房)
 $433万
 $16,654/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -19323,7 +19323,7 @@
           <t>L | 390呎 (2房)
 $666万
 $17,087/呎
-(24年-08月-14日)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
           <t>A | 666呎 (3房)
 $1464万
 $21,977/呎
-(24年-08月-21日)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -19346,7 +19346,7 @@
           <t>B | 382呎 (2房)
 $792万
 $20,730/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -19354,7 +19354,7 @@
           <t>C | 579呎 (3房)
 $1200万
 $20,731/呎
-(24年-08月-15日)</t>
+(24年-08月-16日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -19362,7 +19362,7 @@
           <t>D | 263呎 (1房)
 $488万
 $18,567/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -19370,7 +19370,7 @@
           <t>E | 383呎 (2房)
 $675万
 $17,632/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -19378,7 +19378,7 @@
           <t>F | 382呎 (2房)
 $660万
 $17,291/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -19386,7 +19386,7 @@
           <t>G | 395呎 (2房)
 $674万
 $17,051/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -19394,7 +19394,7 @@
           <t>H | 394呎 (2房)
 $661万
 $16,779/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -19402,7 +19402,7 @@
           <t>J | 261呎 (1房)
 $438万
 $16,778/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -19410,7 +19410,7 @@
           <t>K | 260呎 (1房)
 $432万
 $16,604/呎
-(24年-08月-15日)</t>
+(24年-08月-16日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -19418,7 +19418,7 @@
           <t>L | 390呎 (2房)
 $664万
 $17,036/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -19433,7 +19433,7 @@
           <t>A | 666呎 (3房)
 $1449万
 $21,761/呎
-(24年-09月-10日)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -19441,7 +19441,7 @@
           <t>B | 382呎 (2房)
 $784万
 $20,526/呎
-(24年-08月-14日)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -19449,7 +19449,7 @@
           <t>C | 579呎 (3房)
 $1188万
 $20,527/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -19457,7 +19457,7 @@
           <t>D | 263呎 (1房)
 $467万
 $17,753/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -19465,7 +19465,7 @@
           <t>E | 383呎 (2房)
 $670万
 $17,507/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -19473,7 +19473,7 @@
           <t>F | 382呎 (2房)
 $656万
 $17,165/呎
-(24年-10月-03日)</t>
+(24年-10月-04日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -19481,7 +19481,7 @@
           <t>G | 395呎 (2房)
 $674万
 $17,068/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -19489,7 +19489,7 @@
           <t>H | 394呎 (2房)
 $659万
 $16,726/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -19497,7 +19497,7 @@
           <t>J | 261呎 (1房)
 $554万
 $21,245/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -19505,7 +19505,7 @@
           <t>K | 260呎 (1房)
 $449万
 $17,262/呎
-(24年-08月-25日)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -19513,7 +19513,7 @@
           <t>L | 390呎 (2房)
 $662万
 $16,985/呎
-(24年-09月-01日)</t>
+(24年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -19528,7 +19528,7 @@
           <t>A | 666呎 (3房)
 $1383万
 $20,766/呎
-(24年-12月-04日)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -19536,7 +19536,7 @@
           <t>B | 382呎 (2房)
 $813万
 $21,293/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -19544,7 +19544,7 @@
           <t>C | 579呎 (3房)
 $1183万
 $20,425/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -19552,7 +19552,7 @@
           <t>D | 263呎 (1房)
 $465万
 $17,696/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -19560,7 +19560,7 @@
           <t>E | 383呎 (2房)
 $671万
 $17,527/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -19568,7 +19568,7 @@
           <t>F | 382呎 (2房)
 $657万
 $17,188/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -19576,7 +19576,7 @@
           <t>G | 395呎 (2房)
 $672万
 $17,018/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -19584,7 +19584,7 @@
           <t>H | 394呎 (2房)
 $657万
 $16,678/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -19592,7 +19592,7 @@
           <t>J | 261呎 (1房)
 $435万
 $16,674/呎
-(24年-08月-13日)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -19600,7 +19600,7 @@
           <t>K | 260呎 (1房)
 $429万
 $16,504/呎
-(24年-08月-25日)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -19608,7 +19608,7 @@
           <t>L | 390呎 (2房)
 $660万
 $16,931/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
     </row>
@@ -19623,7 +19623,7 @@
           <t>A | 666呎 (3房)
 $1363万
 $20,470/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -19631,7 +19631,7 @@
           <t>B | 382呎 (2房)
 $776万
 $20,319/呎
-(24年-08月-18日)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -19639,7 +19639,7 @@
           <t>C | 579呎 (3房)
 $1177万
 $20,323/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -19647,7 +19647,7 @@
           <t>D | 263呎 (1房)
 $464万
 $17,643/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -19655,7 +19655,7 @@
           <t>E | 383呎 (2房)
 $669万
 $17,475/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -19663,7 +19663,7 @@
           <t>F | 382呎 (2房)
 $655万
 $17,136/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -19671,7 +19671,7 @@
           <t>G | 395呎 (2房)
 $670万
 $16,967/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -19679,7 +19679,7 @@
           <t>H | 394呎 (2房)
 $642万
 $16,302/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -19687,7 +19687,7 @@
           <t>J | 261呎 (1房)
 $434万
 $16,625/呎
-(24年-09月-10日)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -19695,7 +19695,7 @@
           <t>K | 260呎 (1房)
 $427万
 $16,438/呎
-(24年-09月-10日)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -19703,7 +19703,7 @@
           <t>L | 390呎 (2房)
 $658万
 $16,882/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -19718,7 +19718,7 @@
           <t>A | 628呎 (3房)
 $1597万
 $25,428/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -19726,7 +19726,7 @@
           <t>B | 344呎 (2房)
 $739万
 $21,494/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -19734,7 +19734,7 @@
           <t>C | 579呎 (3房)
 $1158万
 $20,000/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -19742,7 +19742,7 @@
           <t>D | 263呎 (1房)
 $463万
 $17,589/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -19750,7 +19750,7 @@
           <t>E | 383呎 (2房)
 $654万
 $17,089/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -19758,7 +19758,7 @@
           <t>F | 382呎 (2房)
 $648万
 $16,969/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -19766,7 +19766,7 @@
           <t>G | 395呎 (2房)
 $643万
 $16,271/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -19774,7 +19774,7 @@
           <t>H | 394呎 (2房)
 $640万
 $16,254/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -19782,7 +19782,7 @@
           <t>J | 224呎 (1房)
 $425万
 $18,960/呎
-(24年-08月-14日)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -19790,7 +19790,7 @@
           <t>K | 223呎 (1房)
 $438万
 $19,619/呎
-(24年-08月-15日)</t>
+(24年-08月-16日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -19798,7 +19798,7 @@
           <t>L | 390呎 (2房)
 $656万
 $16,831/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-柏蔚森 III/柏蔚森 III_销控明细表.xlsx
+++ b/九龙-启德-柏蔚森 III/柏蔚森 III_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,18 +122,12 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -207,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -269,13 +263,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,7 +758,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -775,31 +766,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
-        <v>8815000</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>22603</v>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>7228300</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>18534</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>150天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1224,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1234,10 +1233,10 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6547000</v>
+        <v>8903000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>24894</v>
+        <v>33852</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1245,14 +1244,14 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5368540</v>
+        <v>7300460</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>20413</v>
+        <v>27758</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>150天現金優惠付款計劃</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -10439,7 +10438,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -10447,31 +10446,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H155" s="5" t="n">
-        <v>10070000</v>
-      </c>
-      <c r="I155" s="5" t="n">
-        <v>26361</v>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="K155" s="5" t="n">
-        <v>8257400</v>
-      </c>
-      <c r="L155" s="5" t="n">
-        <v>21616</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>150天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N155" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17436,7 +17443,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17451,7 +17458,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -17555,9 +17562,9 @@
       <c r="E5" s="21" t="inlineStr">
         <is>
           <t>D | 263呎 (1房)
-$655万
-$24,894/呎
-(暂停销售)</t>
+$890万
+$33,852/呎
+(在售)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -17611,9 +17618,9 @@
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t>L | 390呎 (2房)
-$882万
-$22,603/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -17813,7 +17820,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 666呎 (3房)
 招标单位
@@ -17821,7 +17828,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 382呎 (2房)
 招标单位
@@ -17829,7 +17836,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 579呎 (3房)
 招标单位
@@ -17908,7 +17915,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 666呎 (3房)
 招标单位
@@ -17916,7 +17923,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 382呎 (2房)
 招标单位
@@ -17924,7 +17931,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 579呎 (3房)
 招标单位
@@ -18011,7 +18018,7 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 382呎 (2房)
 招标单位
@@ -18019,7 +18026,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 579呎 (3房)
 招标单位
@@ -18098,7 +18105,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 666呎 (3房)
 招标单位
@@ -18106,7 +18113,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 382呎 (2房)
 招标单位
@@ -18193,7 +18200,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 666呎 (3房)
 招标单位
@@ -18296,7 +18303,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 382呎 (2房)
 招标单位
@@ -18391,7 +18398,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 382呎 (2房)
 招标单位
@@ -18774,9 +18781,9 @@
       <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 382呎 (2房)
-$1007万
-$26,361/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">

--- a/九龙-启德-柏蔚森 III/柏蔚森 III_销控明细表.xlsx
+++ b/九龙-启德-柏蔚森 III/柏蔚森 III_销控明细表.xlsx
@@ -12621,7 +12621,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -19235,7 +19235,7 @@
           <t>L | 390呎 (2房)
 $842万
 $21,595/呎
-(26年-07月-23日)</t>
+(26年-08月-20日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-柏蔚森 III/柏蔚森 III_销控明细表.xlsx
+++ b/九龙-启德-柏蔚森 III/柏蔚森 III_销控明细表.xlsx
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>4772000</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>18144</v>
+        <v>18076</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>4772000</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>18144</v>
+        <v>18076</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -18891,9 +18891,9 @@
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>D | 263呎 (1房)
+          <t>D | 264呎 (1房)
 $477万
-$18,144/呎
+$18,076/呎
 (24年-09月-03日)</t>
         </is>
       </c>
